--- a/docs/data/jp/xlsx/4771.xlsx
+++ b/docs/data/jp/xlsx/4771.xlsx
@@ -2202,7 +2202,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Accounting Service Income Reportable Segments</t>
+          <t>회계 서비스 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2484,7 +2484,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Consulting Income Reportable Segments</t>
+          <t>컨설팅 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -2766,7 +2766,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Business Solution Income Reportable Segments</t>
+          <t>비즈니스 솔루션 사업</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -3330,7 +3330,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>System Development Income Reportable Segments</t>
+          <t>시스템 개발 사업</t>
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>Amortization Of Negative Goodwill NOI</t>
+          <t>부의 영업권 상각액</t>
         </is>
       </c>
       <c r="T116" s="20" t="n">
@@ -9840,7 +9840,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Gain On Forfeiture Of Unclaimed Dividends</t>
+          <t>시효 소멸 배당금 수입</t>
         </is>
       </c>
       <c r="C117" s="20" t="n">
@@ -11914,7 +11914,7 @@
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>회계 서비스 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C157" s="20" t="n">
@@ -12022,7 +12022,7 @@
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>컨설팅 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C159" s="20" t="n">
@@ -12130,7 +12130,7 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>비즈니스 솔루션 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C161" s="20" t="n">
@@ -12346,7 +12346,7 @@
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>시스템 개발 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C165" s="20" t="n">
@@ -12778,7 +12778,7 @@
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>회계 서비스 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C173" s="20" t="n">
@@ -12830,7 +12830,7 @@
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>컨설팅 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C174" s="20" t="n">
@@ -12882,7 +12882,7 @@
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>비즈니스 솔루션 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C175" s="20" t="n">
@@ -12986,7 +12986,7 @@
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>시스템 개발 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C177" s="20" t="n">
@@ -13194,7 +13194,7 @@
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>회계 서비스 사업 · 계</t>
         </is>
       </c>
       <c r="C181" s="20" t="n">
@@ -13302,7 +13302,7 @@
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>컨설팅 사업 · 계</t>
         </is>
       </c>
       <c r="C183" s="20" t="n">
@@ -13410,7 +13410,7 @@
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>비즈니스 솔루션 사업 · 계</t>
         </is>
       </c>
       <c r="C185" s="20" t="n">
@@ -13626,7 +13626,7 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>시스템 개발 사업 · 계</t>
         </is>
       </c>
       <c r="C189" s="20" t="n">
@@ -14058,7 +14058,7 @@
     <row r="197">
       <c r="A197" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>회계 서비스 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C197" s="20" t="n">
@@ -14238,7 +14238,7 @@
     <row r="200">
       <c r="A200" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>컨설팅 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C200" s="20" t="n">
@@ -14418,7 +14418,7 @@
     <row r="203">
       <c r="A203" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>비즈니스 솔루션 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C203" s="20" t="n">
@@ -14778,7 +14778,7 @@
     <row r="209">
       <c r="A209" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>시스템 개발 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C209" s="20" t="n">
@@ -16047,7 +16047,7 @@
     <row r="233">
       <c r="A233" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Sales Of Property Plant And Equipment And Intangible Assets Ope CF</t>
+          <t>유·무형자산 처분손익</t>
         </is>
       </c>
       <c r="D233" s="20" t="n">
@@ -16075,7 +16075,7 @@
     <row r="234">
       <c r="A234" s="18" t="inlineStr">
         <is>
-          <t>Loss On Retirement Of Property Plant And Equipment And Intangible Assets Ope CF</t>
+          <t>유·무형자산 폐기손실</t>
         </is>
       </c>
       <c r="D234" s="20" t="n">
@@ -16278,7 +16278,7 @@
     <row r="239">
       <c r="A239" s="18" t="inlineStr">
         <is>
-          <t>Amount Of ADecrease Of Other Trade Assets Ope CF</t>
+          <t>기타 영업자산의 감소액</t>
         </is>
       </c>
       <c r="O239" s="20" t="n">
@@ -16294,7 +16294,7 @@
     <row r="240">
       <c r="A240" s="18" t="inlineStr">
         <is>
-          <t>Amount Of AIncrease Decrease Of Other Business Debt Ope CF</t>
+          <t>기타 영업부채의 증감액</t>
         </is>
       </c>
       <c r="O240" s="20" t="n">
@@ -17084,7 +17084,7 @@
     <row r="262">
       <c r="A262" s="18" t="inlineStr">
         <is>
-          <t>Expense Of Insurance Savings Inv CF</t>
+          <t>보험적립금 지출</t>
         </is>
       </c>
       <c r="D262" s="20" t="n">
@@ -21202,7 +21202,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Long Term Account Receivable IOA</t>
+          <t>장기체류채권</t>
         </is>
       </c>
       <c r="E101" s="20" t="n">
@@ -21227,7 +21227,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Long Term Account Receivable Fixed Assets</t>
+          <t>장기체류채권</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
@@ -21981,7 +21981,7 @@
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>Negative Goodwill</t>
+          <t>부의 영업권</t>
         </is>
       </c>
       <c r="C127" s="20" t="n">
